--- a/docs/espacio-aprendizaje/indicadores-cruce-tematico.xlsx
+++ b/docs/espacio-aprendizaje/indicadores-cruce-tematico.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cruce Tematico'!$A$1:$I$170</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Propuesta Consolidada'!$A$1:$G$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Propuesta Consolidada'!$A$1:$G$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -44,7 +44,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -99,6 +99,12 @@
         <bgColor rgb="00BBDEFB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
+        <bgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -118,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -168,6 +174,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8549,7 +8558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10966,8 +10975,267 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>QA-65</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Presencia docente e interacción instructor-estudiante</t>
+        </is>
+      </c>
+      <c r="D66" s="22" t="inlineStr">
+        <is>
+          <t>El/la docente publica anuncios regulares y relevantes en el sitio del curso, mantiene presencia activa en foros y actividades asincrónicas, y contribuye significativamente a las discusiones.</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>OLC2025-D3,D4 [GAP cubierto]</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="G66" s="18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>QA-66</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Evaluación, retroalimentación y calificaciones</t>
+        </is>
+      </c>
+      <c r="D67" s="22" t="inlineStr">
+        <is>
+          <t>El/la docente proporciona retroalimentación y califica las evaluaciones dentro de plazos razonables, comunicados previamente a los estudiantes.</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>OLC2025-D6 [GAP cubierto]</t>
+        </is>
+      </c>
+      <c r="F67" s="17" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="G67" s="20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>QA-67</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Competencias docentes para la virtualidad</t>
+        </is>
+      </c>
+      <c r="D68" s="22" t="inlineStr">
+        <is>
+          <t>El/la docente identifica y acompaña proactivamente a los estudiantes que muestran dificultades o riesgo de abandono en el curso.</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>OLC2025-D7 [GAP cubierto]</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="G68" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>QA-68</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Competencias docentes para la virtualidad</t>
+        </is>
+      </c>
+      <c r="D69" s="22" t="inlineStr">
+        <is>
+          <t>El/la docente ajusta contenidos, actividades y fechas en respuesta a las necesidades emergentes del estudiantado, y proporciona síntesis de cierre al finalizar cada módulo o unidad.</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>OLC2025-D11,D13 [GAP cubierto]</t>
+        </is>
+      </c>
+      <c r="F69" s="19" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="G69" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>QA-69</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Requisitos tecnológicos y competencias digitales</t>
+        </is>
+      </c>
+      <c r="D70" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye un diagnóstico de preparación tecnológica previo al inicio (lista de comprobación de requisitos técnicos y/o cuestionario de preparación en línea).</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>OLC2025-A2 [GAP cubierto]</t>
+        </is>
+      </c>
+      <c r="F70" s="19" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="G70" s="18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>QA-70</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Actividades de aprendizaje e interacción</t>
+        </is>
+      </c>
+      <c r="D71" s="22" t="inlineStr">
+        <is>
+          <t>El curso incorpora, cuando la plataforma lo permite, estrategias de aprendizaje adaptativo que personalicen la experiencia según el desempeño del estudiante (actividades condicionales, rutas alternativas).</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>OLC2025-A9 [GAP cubierto]</t>
+        </is>
+      </c>
+      <c r="F71" s="19" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="G71" s="18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>QA-71</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Presencia docente e interacción instructor-estudiante</t>
+        </is>
+      </c>
+      <c r="D72" s="22" t="inlineStr">
+        <is>
+          <t>El/la docente utiliza un lenguaje de apoyo y empático en toda retroalimentación y comunicación, e incorpora ejemplos o experiencias personales que humanicen el contenido del curso.</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>OLC2025-D8,D15 [GAP cubierto]</t>
+        </is>
+      </c>
+      <c r="F72" s="19" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="G72" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G65"/>
+  <autoFilter ref="A1:G72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11766,7 +12034,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -11810,7 +12077,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
@@ -11854,7 +12120,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
@@ -11898,7 +12163,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
@@ -11942,8 +12206,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>

--- a/docs/espacio-aprendizaje/indicadores-cruce-tematico.xlsx
+++ b/docs/espacio-aprendizaje/indicadores-cruce-tematico.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leyenda" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cruce Tematico'!$A$1:$I$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cruce Tematico'!$A$1:$I$220</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Propuesta Consolidada'!$A$1:$G$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44,7 +44,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -105,6 +105,12 @@
         <bgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCEDC8"/>
+        <bgColor rgb="00DCEDC8"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -124,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -178,6 +184,19 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -543,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I170"/>
+  <dimension ref="A1:I220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8546,8 +8565,2358 @@
         </is>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Objetivos y resultados de aprendizaje</t>
+        </is>
+      </c>
+      <c r="C171" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D171" s="22" t="inlineStr">
+        <is>
+          <t>OLC-E-1</t>
+        </is>
+      </c>
+      <c r="E171" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Esencial</t>
+        </is>
+      </c>
+      <c r="F171" s="22" t="inlineStr">
+        <is>
+          <t>Los objetivos y/o resultados del aprendizaje son específicos, mensurables y están claramente definidos.</t>
+        </is>
+      </c>
+      <c r="G171" s="22" t="inlineStr">
+        <is>
+          <t>Los objetivos y/o resultados del aprendizaje son específicos, mensurables y están claramente definidos.</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Esencial</t>
+        </is>
+      </c>
+      <c r="I171" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Requisitos tecnológicos y competencias digitales</t>
+        </is>
+      </c>
+      <c r="C172" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D172" s="22" t="inlineStr">
+        <is>
+          <t>OLC-E-2</t>
+        </is>
+      </c>
+      <c r="E172" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Esencial</t>
+        </is>
+      </c>
+      <c r="F172" s="22" t="inlineStr">
+        <is>
+          <t>El curso enumera todos los materiales de aprendizaje necesarios, incluidas las herramientas tecnológicas.</t>
+        </is>
+      </c>
+      <c r="G172" s="22" t="inlineStr">
+        <is>
+          <t>El curso enumera todos los materiales de aprendizaje necesarios, incluidas las herramientas tecnológicas.</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Esencial</t>
+        </is>
+      </c>
+      <c r="I172" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Presencia docente e interacción instructor-estudiante</t>
+        </is>
+      </c>
+      <c r="C173" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D173" s="22" t="inlineStr">
+        <is>
+          <t>OLC-E-3</t>
+        </is>
+      </c>
+      <c r="E173" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Esencial</t>
+        </is>
+      </c>
+      <c r="F173" s="22" t="inlineStr">
+        <is>
+          <t>El curso proporciona horas de oficina, preferencias de comunicación y tiempos de respuesta.</t>
+        </is>
+      </c>
+      <c r="G173" s="22" t="inlineStr">
+        <is>
+          <t>El curso proporciona horas de oficina, preferencias de comunicación y tiempos de respuesta.</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Esencial</t>
+        </is>
+      </c>
+      <c r="I173" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Soporte al estudiante y servicios institucionales</t>
+        </is>
+      </c>
+      <c r="C174" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D174" s="22" t="inlineStr">
+        <is>
+          <t>OLC-E-4</t>
+        </is>
+      </c>
+      <c r="E174" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Esencial</t>
+        </is>
+      </c>
+      <c r="F174" s="22" t="inlineStr">
+        <is>
+          <t>El curso proporciona recursos de soporte técnico y ayuda para problemas técnicos comunes.</t>
+        </is>
+      </c>
+      <c r="G174" s="22" t="inlineStr">
+        <is>
+          <t>El curso proporciona recursos de soporte técnico y ayuda para problemas técnicos comunes.</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Esencial</t>
+        </is>
+      </c>
+      <c r="I174" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Requisitos tecnológicos y competencias digitales</t>
+        </is>
+      </c>
+      <c r="C175" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D175" s="22" t="inlineStr">
+        <is>
+          <t>OLC-E-5</t>
+        </is>
+      </c>
+      <c r="E175" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Esencial</t>
+        </is>
+      </c>
+      <c r="F175" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye guías o tutoriales paso a paso para todas las tecnologías necesarias.</t>
+        </is>
+      </c>
+      <c r="G175" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye guías o tutoriales paso a paso para todas las tecnologías necesarias.</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Esencial</t>
+        </is>
+      </c>
+      <c r="I175" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Políticas institucionales y normas académicas</t>
+        </is>
+      </c>
+      <c r="C176" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D176" s="22" t="inlineStr">
+        <is>
+          <t>OLC-E-6</t>
+        </is>
+      </c>
+      <c r="E176" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Esencial</t>
+        </is>
+      </c>
+      <c r="F176" s="22" t="inlineStr">
+        <is>
+          <t>El curso define las políticas de calificación, las expectativas de integridad académica y las políticas sobre retrasos.</t>
+        </is>
+      </c>
+      <c r="G176" s="22" t="inlineStr">
+        <is>
+          <t>El curso define las políticas de calificación, las expectativas de integridad académica y las políticas sobre retrasos.</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Esencial</t>
+        </is>
+      </c>
+      <c r="I176" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Accesibilidad multimodal y DUA</t>
+        </is>
+      </c>
+      <c r="C177" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D177" s="22" t="inlineStr">
+        <is>
+          <t>OLC-E-7</t>
+        </is>
+      </c>
+      <c r="E177" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Esencial</t>
+        </is>
+      </c>
+      <c r="F177" s="22" t="inlineStr">
+        <is>
+          <t>El curso proporciona una declaración de accesibilidad y los pasos para solicitar adaptaciones.</t>
+        </is>
+      </c>
+      <c r="G177" s="22" t="inlineStr">
+        <is>
+          <t>El curso proporciona una declaración de accesibilidad y los pasos para solicitar adaptaciones.</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Esencial</t>
+        </is>
+      </c>
+      <c r="I177" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Soporte al estudiante y servicios institucionales</t>
+        </is>
+      </c>
+      <c r="C178" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D178" s="22" t="inlineStr">
+        <is>
+          <t>OLC-E-8</t>
+        </is>
+      </c>
+      <c r="E178" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Esencial</t>
+        </is>
+      </c>
+      <c r="F178" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye información sobre los servicios de apoyo al estudiante y otros servicios.</t>
+        </is>
+      </c>
+      <c r="G178" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye información sobre los servicios de apoyo al estudiante y otros servicios.</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Esencial</t>
+        </is>
+      </c>
+      <c r="I178" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>T01</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Bienvenida, orientación e información del curso</t>
+        </is>
+      </c>
+      <c r="C179" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D179" s="22" t="inlineStr">
+        <is>
+          <t>OLC-E-9</t>
+        </is>
+      </c>
+      <c r="E179" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Esencial</t>
+        </is>
+      </c>
+      <c r="F179" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye un calendario con las fechas de entrega de todas las tareas y actividades.</t>
+        </is>
+      </c>
+      <c r="G179" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye un calendario con las fechas de entrega de todas las tareas y actividades.</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Esencial</t>
+        </is>
+      </c>
+      <c r="I179" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Actividades de aprendizaje e interacción</t>
+        </is>
+      </c>
+      <c r="C180" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D180" s="22" t="inlineStr">
+        <is>
+          <t>OLC-E-10</t>
+        </is>
+      </c>
+      <c r="E180" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Esencial</t>
+        </is>
+      </c>
+      <c r="F180" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye un debate introductorio y directrices para la interacción de los estudiantes.</t>
+        </is>
+      </c>
+      <c r="G180" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye un debate introductorio y directrices para la interacción de los estudiantes.</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Esencial</t>
+        </is>
+      </c>
+      <c r="I180" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Navegación, diseño y estructura visual</t>
+        </is>
+      </c>
+      <c r="C181" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D181" s="22" t="inlineStr">
+        <is>
+          <t>OLC-E-11</t>
+        </is>
+      </c>
+      <c r="E181" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Esencial</t>
+        </is>
+      </c>
+      <c r="F181" s="22" t="inlineStr">
+        <is>
+          <t>La navegación y el diseño del sitio del curso son claros y coherentes.</t>
+        </is>
+      </c>
+      <c r="G181" s="22" t="inlineStr">
+        <is>
+          <t>La navegación y el diseño del sitio del curso son claros y coherentes.</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Esencial</t>
+        </is>
+      </c>
+      <c r="I181" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Contenidos y materiales instruccionales</t>
+        </is>
+      </c>
+      <c r="C182" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D182" s="22" t="inlineStr">
+        <is>
+          <t>OLC-E-12</t>
+        </is>
+      </c>
+      <c r="E182" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Esencial</t>
+        </is>
+      </c>
+      <c r="F182" s="22" t="inlineStr">
+        <is>
+          <t>Los vídeos y otros contenidos multimedia son de calidad y duración adecuadas.</t>
+        </is>
+      </c>
+      <c r="G182" s="22" t="inlineStr">
+        <is>
+          <t>Los vídeos y otros contenidos multimedia son de calidad y duración adecuadas.</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Esencial</t>
+        </is>
+      </c>
+      <c r="I182" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Contenidos y materiales instruccionales</t>
+        </is>
+      </c>
+      <c r="C183" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D183" s="22" t="inlineStr">
+        <is>
+          <t>OLC-E-13</t>
+        </is>
+      </c>
+      <c r="E183" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Esencial</t>
+        </is>
+      </c>
+      <c r="F183" s="22" t="inlineStr">
+        <is>
+          <t>El contenido del curso está actualizado, es relevante y está vinculado a objetivos de aprendizaje específicos.</t>
+        </is>
+      </c>
+      <c r="G183" s="22" t="inlineStr">
+        <is>
+          <t>El contenido del curso está actualizado, es relevante y está vinculado a objetivos de aprendizaje específicos.</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Esencial</t>
+        </is>
+      </c>
+      <c r="I183" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Evaluación, retroalimentación y calificaciones</t>
+        </is>
+      </c>
+      <c r="C184" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D184" s="22" t="inlineStr">
+        <is>
+          <t>OLC-E-14</t>
+        </is>
+      </c>
+      <c r="E184" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Esencial</t>
+        </is>
+      </c>
+      <c r="F184" s="22" t="inlineStr">
+        <is>
+          <t>El sitio del curso proporciona un libro de calificaciones organizado que incluye todas las evaluaciones.</t>
+        </is>
+      </c>
+      <c r="G184" s="22" t="inlineStr">
+        <is>
+          <t>El sitio del curso proporciona un libro de calificaciones organizado que incluye todas las evaluaciones.</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Esencial</t>
+        </is>
+      </c>
+      <c r="I184" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Evaluación, retroalimentación y calificaciones</t>
+        </is>
+      </c>
+      <c r="C185" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D185" s="22" t="inlineStr">
+        <is>
+          <t>OLC-E-15</t>
+        </is>
+      </c>
+      <c r="E185" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Esencial</t>
+        </is>
+      </c>
+      <c r="F185" s="22" t="inlineStr">
+        <is>
+          <t>El curso incorpora evaluaciones formativas de baja exigencia para un compromiso frecuente.</t>
+        </is>
+      </c>
+      <c r="G185" s="22" t="inlineStr">
+        <is>
+          <t>El curso incorpora evaluaciones formativas de baja exigencia para un compromiso frecuente.</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Esencial</t>
+        </is>
+      </c>
+      <c r="I185" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Evaluación, retroalimentación y calificaciones</t>
+        </is>
+      </c>
+      <c r="C186" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D186" s="22" t="inlineStr">
+        <is>
+          <t>OLC-E-16</t>
+        </is>
+      </c>
+      <c r="E186" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Esencial</t>
+        </is>
+      </c>
+      <c r="F186" s="22" t="inlineStr">
+        <is>
+          <t>El curso proporciona un enfoque de andamiaje para las evaluaciones sumativas.</t>
+        </is>
+      </c>
+      <c r="G186" s="22" t="inlineStr">
+        <is>
+          <t>El curso proporciona un enfoque de andamiaje para las evaluaciones sumativas.</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Esencial</t>
+        </is>
+      </c>
+      <c r="I186" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Contenidos y materiales instruccionales</t>
+        </is>
+      </c>
+      <c r="C187" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D187" s="22" t="inlineStr">
+        <is>
+          <t>OLC-E-17</t>
+        </is>
+      </c>
+      <c r="E187" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Esencial</t>
+        </is>
+      </c>
+      <c r="F187" s="22" t="inlineStr">
+        <is>
+          <t>Todos los módulos, tareas y actividades incluyen instrucciones claras y detalladas.</t>
+        </is>
+      </c>
+      <c r="G187" s="22" t="inlineStr">
+        <is>
+          <t>Todos los módulos, tareas y actividades incluyen instrucciones claras y detalladas.</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Esencial</t>
+        </is>
+      </c>
+      <c r="I187" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>Evaluación, retroalimentación y calificaciones</t>
+        </is>
+      </c>
+      <c r="C188" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D188" s="22" t="inlineStr">
+        <is>
+          <t>OLC-E-18</t>
+        </is>
+      </c>
+      <c r="E188" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Esencial</t>
+        </is>
+      </c>
+      <c r="F188" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye rúbricas para todas las tareas y evaluaciones.</t>
+        </is>
+      </c>
+      <c r="G188" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye rúbricas para todas las tareas y evaluaciones.</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Esencial</t>
+        </is>
+      </c>
+      <c r="I188" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>T18</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Bienestar, cuidados digitales y corresponsabilidad</t>
+        </is>
+      </c>
+      <c r="C189" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D189" s="22" t="inlineStr">
+        <is>
+          <t>OLC-E-19</t>
+        </is>
+      </c>
+      <c r="E189" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Esencial</t>
+        </is>
+      </c>
+      <c r="F189" s="22" t="inlineStr">
+        <is>
+          <t>La carga de trabajo del curso es equilibrada y apropiada para la disciplina y el nivel del curso.</t>
+        </is>
+      </c>
+      <c r="G189" s="22" t="inlineStr">
+        <is>
+          <t>La carga de trabajo del curso es equilibrada y apropiada para la disciplina y el nivel del curso.</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Esencial</t>
+        </is>
+      </c>
+      <c r="I189" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Funcionalidad técnica de la plataforma</t>
+        </is>
+      </c>
+      <c r="C190" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D190" s="22" t="inlineStr">
+        <is>
+          <t>OLC-E-20</t>
+        </is>
+      </c>
+      <c r="E190" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Esencial</t>
+        </is>
+      </c>
+      <c r="F190" s="22" t="inlineStr">
+        <is>
+          <t>Los materiales del curso no contienen enlaces rotos, errores ortográficos ni información incorrecta.</t>
+        </is>
+      </c>
+      <c r="G190" s="22" t="inlineStr">
+        <is>
+          <t>Los materiales del curso no contienen enlaces rotos, errores ortográficos ni información incorrecta.</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Esencial</t>
+        </is>
+      </c>
+      <c r="I190" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Objetivos y resultados de aprendizaje</t>
+        </is>
+      </c>
+      <c r="C191" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D191" s="22" t="inlineStr">
+        <is>
+          <t>OLC-A-1</t>
+        </is>
+      </c>
+      <c r="E191" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Avanzado</t>
+        </is>
+      </c>
+      <c r="F191" s="22" t="inlineStr">
+        <is>
+          <t>Los objetivos y/o resultados de aprendizaje del curso utilizan un lenguaje centrado en el alumno.</t>
+        </is>
+      </c>
+      <c r="G191" s="22" t="inlineStr">
+        <is>
+          <t>Los objetivos y/o resultados de aprendizaje del curso utilizan un lenguaje centrado en el alumno.</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Avanzado</t>
+        </is>
+      </c>
+      <c r="I191" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Requisitos tecnológicos y competencias digitales</t>
+        </is>
+      </c>
+      <c r="C192" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D192" s="22" t="inlineStr">
+        <is>
+          <t>OLC-A-2</t>
+        </is>
+      </c>
+      <c r="E192" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Avanzado</t>
+        </is>
+      </c>
+      <c r="F192" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye una lista de comprobación tecnológica previa al curso y un cuestionario de preparación en línea.</t>
+        </is>
+      </c>
+      <c r="G192" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye una lista de comprobación tecnológica previa al curso y un cuestionario de preparación en línea.</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Avanzado</t>
+        </is>
+      </c>
+      <c r="I192" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>T01</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>Bienvenida, orientación e información del curso</t>
+        </is>
+      </c>
+      <c r="C193" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D193" s="22" t="inlineStr">
+        <is>
+          <t>OLC-A-3</t>
+        </is>
+      </c>
+      <c r="E193" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Avanzado</t>
+        </is>
+      </c>
+      <c r="F193" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye un módulo de orientación, un vídeo o una guía para navegar por el curso.</t>
+        </is>
+      </c>
+      <c r="G193" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye un módulo de orientación, un vídeo o una guía para navegar por el curso.</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Avanzado</t>
+        </is>
+      </c>
+      <c r="I193" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>Políticas institucionales y normas académicas</t>
+        </is>
+      </c>
+      <c r="C194" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D194" s="22" t="inlineStr">
+        <is>
+          <t>OLC-A-4</t>
+        </is>
+      </c>
+      <c r="E194" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Avanzado</t>
+        </is>
+      </c>
+      <c r="F194" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye directrices explícitas para el uso de la IA generativa.</t>
+        </is>
+      </c>
+      <c r="G194" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye directrices explícitas para el uso de la IA generativa.</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Avanzado</t>
+        </is>
+      </c>
+      <c r="I194" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>Recursos educativos abiertos (REA) y licencias</t>
+        </is>
+      </c>
+      <c r="C195" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D195" s="22" t="inlineStr">
+        <is>
+          <t>OLC-A-5</t>
+        </is>
+      </c>
+      <c r="E195" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Avanzado</t>
+        </is>
+      </c>
+      <c r="F195" s="22" t="inlineStr">
+        <is>
+          <t>El curso utiliza exclusivamente materiales de bajo coste o gratuitos.</t>
+        </is>
+      </c>
+      <c r="G195" s="22" t="inlineStr">
+        <is>
+          <t>El curso utiliza exclusivamente materiales de bajo coste o gratuitos.</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Avanzado</t>
+        </is>
+      </c>
+      <c r="I195" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Actividades de aprendizaje e interacción</t>
+        </is>
+      </c>
+      <c r="C196" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D196" s="22" t="inlineStr">
+        <is>
+          <t>OLC-A-6</t>
+        </is>
+      </c>
+      <c r="E196" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Avanzado</t>
+        </is>
+      </c>
+      <c r="F196" s="22" t="inlineStr">
+        <is>
+          <t>El curso ofrece múltiples vías para que los alumnos alcancen los objetivos de aprendizaje.</t>
+        </is>
+      </c>
+      <c r="G196" s="22" t="inlineStr">
+        <is>
+          <t>El curso ofrece múltiples vías para que los alumnos alcancen los objetivos de aprendizaje.</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Avanzado</t>
+        </is>
+      </c>
+      <c r="I196" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>T17</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>Perspectiva de género, equidad y trato no discriminatorio</t>
+        </is>
+      </c>
+      <c r="C197" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D197" s="22" t="inlineStr">
+        <is>
+          <t>OLC-A-7</t>
+        </is>
+      </c>
+      <c r="E197" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Avanzado</t>
+        </is>
+      </c>
+      <c r="F197" s="22" t="inlineStr">
+        <is>
+          <t>El contenido incluye ejemplos que representan a una amplia gama de alumnos.</t>
+        </is>
+      </c>
+      <c r="G197" s="22" t="inlineStr">
+        <is>
+          <t>El contenido incluye ejemplos que representan a una amplia gama de alumnos.</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Avanzado</t>
+        </is>
+      </c>
+      <c r="I197" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Actividades de aprendizaje e interacción</t>
+        </is>
+      </c>
+      <c r="C198" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D198" s="22" t="inlineStr">
+        <is>
+          <t>OLC-A-8</t>
+        </is>
+      </c>
+      <c r="E198" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Avanzado</t>
+        </is>
+      </c>
+      <c r="F198" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye un foro en línea para los puntos más confusos o las preguntas sobre el curso.</t>
+        </is>
+      </c>
+      <c r="G198" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye un foro en línea para los puntos más confusos o las preguntas sobre el curso.</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Avanzado</t>
+        </is>
+      </c>
+      <c r="I198" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>Actividades de aprendizaje e interacción</t>
+        </is>
+      </c>
+      <c r="C199" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D199" s="22" t="inlineStr">
+        <is>
+          <t>OLC-A-9</t>
+        </is>
+      </c>
+      <c r="E199" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Avanzado</t>
+        </is>
+      </c>
+      <c r="F199" s="22" t="inlineStr">
+        <is>
+          <t>El curso incorpora estrategias de aprendizaje adaptativo para personalizar el aprendizaje.</t>
+        </is>
+      </c>
+      <c r="G199" s="22" t="inlineStr">
+        <is>
+          <t>El curso incorpora estrategias de aprendizaje adaptativo para personalizar el aprendizaje.</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Avanzado</t>
+        </is>
+      </c>
+      <c r="I199" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>Accesibilidad multimodal y DUA</t>
+        </is>
+      </c>
+      <c r="C200" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D200" s="22" t="inlineStr">
+        <is>
+          <t>OLC-A-10</t>
+        </is>
+      </c>
+      <c r="E200" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Avanzado</t>
+        </is>
+      </c>
+      <c r="F200" s="22" t="inlineStr">
+        <is>
+          <t>Los materiales de texto cumplen las normas de accesibilidad y diseño universal.</t>
+        </is>
+      </c>
+      <c r="G200" s="22" t="inlineStr">
+        <is>
+          <t>Los materiales de texto cumplen las normas de accesibilidad y diseño universal.</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Avanzado</t>
+        </is>
+      </c>
+      <c r="I200" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Accesibilidad multimodal y DUA</t>
+        </is>
+      </c>
+      <c r="C201" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D201" s="22" t="inlineStr">
+        <is>
+          <t>OLC-A-11</t>
+        </is>
+      </c>
+      <c r="E201" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Avanzado</t>
+        </is>
+      </c>
+      <c r="F201" s="22" t="inlineStr">
+        <is>
+          <t>Los vídeos y otros contenidos multimedia cumplen las normas de accesibilidad.</t>
+        </is>
+      </c>
+      <c r="G201" s="22" t="inlineStr">
+        <is>
+          <t>Los vídeos y otros contenidos multimedia cumplen las normas de accesibilidad.</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Avanzado</t>
+        </is>
+      </c>
+      <c r="I201" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Actividades de aprendizaje e interacción</t>
+        </is>
+      </c>
+      <c r="C202" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D202" s="22" t="inlineStr">
+        <is>
+          <t>OLC-A-12</t>
+        </is>
+      </c>
+      <c r="E202" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Avanzado</t>
+        </is>
+      </c>
+      <c r="F202" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye formas para que los alumnos contribuyan de manera significativa al contenido del curso.</t>
+        </is>
+      </c>
+      <c r="G202" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye formas para que los alumnos contribuyan de manera significativa al contenido del curso.</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Avanzado</t>
+        </is>
+      </c>
+      <c r="I202" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>Evaluación, retroalimentación y calificaciones</t>
+        </is>
+      </c>
+      <c r="C203" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D203" s="22" t="inlineStr">
+        <is>
+          <t>OLC-A-13</t>
+        </is>
+      </c>
+      <c r="E203" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Avanzado</t>
+        </is>
+      </c>
+      <c r="F203" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye modelos de entregables para las evaluaciones sumativas.</t>
+        </is>
+      </c>
+      <c r="G203" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye modelos de entregables para las evaluaciones sumativas.</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Avanzado</t>
+        </is>
+      </c>
+      <c r="I203" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Evaluación, retroalimentación y calificaciones</t>
+        </is>
+      </c>
+      <c r="C204" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D204" s="22" t="inlineStr">
+        <is>
+          <t>OLC-A-14</t>
+        </is>
+      </c>
+      <c r="E204" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Avanzado</t>
+        </is>
+      </c>
+      <c r="F204" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye evaluaciones con aplicaciones prácticas de palabras reales.</t>
+        </is>
+      </c>
+      <c r="G204" s="22" t="inlineStr">
+        <is>
+          <t>El curso incluye evaluaciones con aplicaciones prácticas de palabras reales.</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Avanzado</t>
+        </is>
+      </c>
+      <c r="I204" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>Evaluación, retroalimentación y calificaciones</t>
+        </is>
+      </c>
+      <c r="C205" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D205" s="22" t="inlineStr">
+        <is>
+          <t>OLC-A-15</t>
+        </is>
+      </c>
+      <c r="E205" s="22" t="inlineStr">
+        <is>
+          <t>Diseño Avanzado</t>
+        </is>
+      </c>
+      <c r="F205" s="22" t="inlineStr">
+        <is>
+          <t>El curso apoya la metacognición del alumno mediante actividades periódicas de autorreflexión.</t>
+        </is>
+      </c>
+      <c r="G205" s="22" t="inlineStr">
+        <is>
+          <t>El curso apoya la metacognición del alumno mediante actividades periódicas de autorreflexión.</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Avanzado</t>
+        </is>
+      </c>
+      <c r="I205" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Presencia docente e interacción instructor-estudiante</t>
+        </is>
+      </c>
+      <c r="C206" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D206" s="22" t="inlineStr">
+        <is>
+          <t>OLC-D-1</t>
+        </is>
+      </c>
+      <c r="E206" s="22" t="inlineStr">
+        <is>
+          <t>Entrega del Curso</t>
+        </is>
+      </c>
+      <c r="F206" s="22" t="inlineStr">
+        <is>
+          <t>El instructor ofrece una introducción personal al curso.</t>
+        </is>
+      </c>
+      <c r="G206" s="22" t="inlineStr">
+        <is>
+          <t>El instructor ofrece una introducción personal al curso.</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Entrega</t>
+        </is>
+      </c>
+      <c r="I206" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Competencias docentes para la virtualidad</t>
+        </is>
+      </c>
+      <c r="C207" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D207" s="22" t="inlineStr">
+        <is>
+          <t>OLC-D-2</t>
+        </is>
+      </c>
+      <c r="E207" s="22" t="inlineStr">
+        <is>
+          <t>Entrega del Curso</t>
+        </is>
+      </c>
+      <c r="F207" s="22" t="inlineStr">
+        <is>
+          <t>El instructor publica módulos y contenidos en el sitio del curso de manera oportuna.</t>
+        </is>
+      </c>
+      <c r="G207" s="22" t="inlineStr">
+        <is>
+          <t>El instructor publica módulos y contenidos en el sitio del curso de manera oportuna.</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Entrega</t>
+        </is>
+      </c>
+      <c r="I207" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>Presencia docente e interacción instructor-estudiante</t>
+        </is>
+      </c>
+      <c r="C208" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D208" s="22" t="inlineStr">
+        <is>
+          <t>OLC-D-3</t>
+        </is>
+      </c>
+      <c r="E208" s="22" t="inlineStr">
+        <is>
+          <t>Entrega del Curso</t>
+        </is>
+      </c>
+      <c r="F208" s="22" t="inlineStr">
+        <is>
+          <t>El instructor publica anuncios regulares y relevantes en el sitio del curso.</t>
+        </is>
+      </c>
+      <c r="G208" s="22" t="inlineStr">
+        <is>
+          <t>El instructor publica anuncios regulares y relevantes en el sitio del curso.</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Entrega</t>
+        </is>
+      </c>
+      <c r="I208" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>Presencia docente e interacción instructor-estudiante</t>
+        </is>
+      </c>
+      <c r="C209" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D209" s="22" t="inlineStr">
+        <is>
+          <t>OLC-D-4</t>
+        </is>
+      </c>
+      <c r="E209" s="22" t="inlineStr">
+        <is>
+          <t>Entrega del Curso</t>
+        </is>
+      </c>
+      <c r="F209" s="22" t="inlineStr">
+        <is>
+          <t>El instructor contribuye significativamente a las actividades y discusiones en línea.</t>
+        </is>
+      </c>
+      <c r="G209" s="22" t="inlineStr">
+        <is>
+          <t>El instructor contribuye significativamente a las actividades y discusiones en línea.</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Entrega</t>
+        </is>
+      </c>
+      <c r="I209" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>Evaluación, retroalimentación y calificaciones</t>
+        </is>
+      </c>
+      <c r="C210" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D210" s="22" t="inlineStr">
+        <is>
+          <t>OLC-D-5</t>
+        </is>
+      </c>
+      <c r="E210" s="22" t="inlineStr">
+        <is>
+          <t>Entrega del Curso</t>
+        </is>
+      </c>
+      <c r="F210" s="22" t="inlineStr">
+        <is>
+          <t>El instructor proporciona retroalimentación específica y dirigida sobre las tareas.</t>
+        </is>
+      </c>
+      <c r="G210" s="22" t="inlineStr">
+        <is>
+          <t>El instructor proporciona retroalimentación específica y dirigida sobre las tareas.</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Entrega</t>
+        </is>
+      </c>
+      <c r="I210" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>Evaluación, retroalimentación y calificaciones</t>
+        </is>
+      </c>
+      <c r="C211" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D211" s="22" t="inlineStr">
+        <is>
+          <t>OLC-D-6</t>
+        </is>
+      </c>
+      <c r="E211" s="22" t="inlineStr">
+        <is>
+          <t>Entrega del Curso</t>
+        </is>
+      </c>
+      <c r="F211" s="22" t="inlineStr">
+        <is>
+          <t>El instructor proporciona retroalimentación y califica las evaluaciones de manera oportuna.</t>
+        </is>
+      </c>
+      <c r="G211" s="22" t="inlineStr">
+        <is>
+          <t>El instructor proporciona retroalimentación y califica las evaluaciones de manera oportuna.</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Entrega</t>
+        </is>
+      </c>
+      <c r="I211" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>Competencias docentes para la virtualidad</t>
+        </is>
+      </c>
+      <c r="C212" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D212" s="22" t="inlineStr">
+        <is>
+          <t>OLC-D-7</t>
+        </is>
+      </c>
+      <c r="E212" s="22" t="inlineStr">
+        <is>
+          <t>Entrega del Curso</t>
+        </is>
+      </c>
+      <c r="F212" s="22" t="inlineStr">
+        <is>
+          <t>El profesor se compromete activamente con los alumnos que muestran dificultades en el curso.</t>
+        </is>
+      </c>
+      <c r="G212" s="22" t="inlineStr">
+        <is>
+          <t>El profesor se compromete activamente con los alumnos que muestran dificultades en el curso.</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Entrega</t>
+        </is>
+      </c>
+      <c r="I212" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>Presencia docente e interacción instructor-estudiante</t>
+        </is>
+      </c>
+      <c r="C213" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D213" s="22" t="inlineStr">
+        <is>
+          <t>OLC-D-8</t>
+        </is>
+      </c>
+      <c r="E213" s="22" t="inlineStr">
+        <is>
+          <t>Entrega del Curso</t>
+        </is>
+      </c>
+      <c r="F213" s="22" t="inlineStr">
+        <is>
+          <t>El instructor utiliza un lenguaje de apoyo en todos los comentarios y comunicaciones.</t>
+        </is>
+      </c>
+      <c r="G213" s="22" t="inlineStr">
+        <is>
+          <t>El instructor utiliza un lenguaje de apoyo en todos los comentarios y comunicaciones.</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Entrega</t>
+        </is>
+      </c>
+      <c r="I213" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>Presencia docente e interacción instructor-estudiante</t>
+        </is>
+      </c>
+      <c r="C214" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D214" s="22" t="inlineStr">
+        <is>
+          <t>OLC-D-9</t>
+        </is>
+      </c>
+      <c r="E214" s="22" t="inlineStr">
+        <is>
+          <t>Entrega del Curso</t>
+        </is>
+      </c>
+      <c r="F214" s="22" t="inlineStr">
+        <is>
+          <t>El instructor anima o incentiva a los alumnos a participar en las horas de oficina.</t>
+        </is>
+      </c>
+      <c r="G214" s="22" t="inlineStr">
+        <is>
+          <t>El instructor anima o incentiva a los alumnos a participar en las horas de oficina.</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Entrega</t>
+        </is>
+      </c>
+      <c r="I214" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>Presencia docente e interacción instructor-estudiante</t>
+        </is>
+      </c>
+      <c r="C215" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D215" s="22" t="inlineStr">
+        <is>
+          <t>OLC-D-10</t>
+        </is>
+      </c>
+      <c r="E215" s="22" t="inlineStr">
+        <is>
+          <t>Entrega del Curso</t>
+        </is>
+      </c>
+      <c r="F215" s="22" t="inlineStr">
+        <is>
+          <t>El instructor responde a las comunicaciones y consultas de los estudiantes de manera oportuna.</t>
+        </is>
+      </c>
+      <c r="G215" s="22" t="inlineStr">
+        <is>
+          <t>El instructor responde a las comunicaciones y consultas de los estudiantes de manera oportuna.</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Entrega</t>
+        </is>
+      </c>
+      <c r="I215" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>Competencias docentes para la virtualidad</t>
+        </is>
+      </c>
+      <c r="C216" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D216" s="22" t="inlineStr">
+        <is>
+          <t>OLC-D-11</t>
+        </is>
+      </c>
+      <c r="E216" s="22" t="inlineStr">
+        <is>
+          <t>Entrega del Curso</t>
+        </is>
+      </c>
+      <c r="F216" s="22" t="inlineStr">
+        <is>
+          <t>El instructor proporciona resúmenes al final del módulo basados en las contribuciones de los alumnos.</t>
+        </is>
+      </c>
+      <c r="G216" s="22" t="inlineStr">
+        <is>
+          <t>El instructor proporciona resúmenes al final del módulo basados en las contribuciones de los alumnos.</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Entrega</t>
+        </is>
+      </c>
+      <c r="I216" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>Actividades de aprendizaje e interacción</t>
+        </is>
+      </c>
+      <c r="C217" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D217" s="22" t="inlineStr">
+        <is>
+          <t>OLC-D-12</t>
+        </is>
+      </c>
+      <c r="E217" s="22" t="inlineStr">
+        <is>
+          <t>Entrega del Curso</t>
+        </is>
+      </c>
+      <c r="F217" s="22" t="inlineStr">
+        <is>
+          <t>El instructor fomenta la participación de alumno a alumno en las actividades en línea.</t>
+        </is>
+      </c>
+      <c r="G217" s="22" t="inlineStr">
+        <is>
+          <t>El instructor fomenta la participación de alumno a alumno en las actividades en línea.</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Entrega</t>
+        </is>
+      </c>
+      <c r="I217" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>Competencias docentes para la virtualidad</t>
+        </is>
+      </c>
+      <c r="C218" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D218" s="22" t="inlineStr">
+        <is>
+          <t>OLC-D-13</t>
+        </is>
+      </c>
+      <c r="E218" s="22" t="inlineStr">
+        <is>
+          <t>Entrega del Curso</t>
+        </is>
+      </c>
+      <c r="F218" s="22" t="inlineStr">
+        <is>
+          <t>El instructor ajusta el contenido, las tareas y las fechas en respuesta a las necesidades del alumno.</t>
+        </is>
+      </c>
+      <c r="G218" s="22" t="inlineStr">
+        <is>
+          <t>El instructor ajusta el contenido, las tareas y las fechas en respuesta a las necesidades del alumno.</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Entrega</t>
+        </is>
+      </c>
+      <c r="I218" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>Evaluación, retroalimentación y calificaciones</t>
+        </is>
+      </c>
+      <c r="C219" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D219" s="22" t="inlineStr">
+        <is>
+          <t>OLC-D-14</t>
+        </is>
+      </c>
+      <c r="E219" s="22" t="inlineStr">
+        <is>
+          <t>Entrega del Curso</t>
+        </is>
+      </c>
+      <c r="F219" s="22" t="inlineStr">
+        <is>
+          <t>El instructor solicita la opinión de los alumnos sobre el curso en varios momentos del curso.</t>
+        </is>
+      </c>
+      <c r="G219" s="22" t="inlineStr">
+        <is>
+          <t>El instructor solicita la opinión de los alumnos sobre el curso en varios momentos del curso.</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Entrega</t>
+        </is>
+      </c>
+      <c r="I219" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>Presencia docente e interacción instructor-estudiante</t>
+        </is>
+      </c>
+      <c r="C220" s="22" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="D220" s="22" t="inlineStr">
+        <is>
+          <t>OLC-D-15</t>
+        </is>
+      </c>
+      <c r="E220" s="22" t="inlineStr">
+        <is>
+          <t>Entrega del Curso</t>
+        </is>
+      </c>
+      <c r="F220" s="22" t="inlineStr">
+        <is>
+          <t>El instructor incorpora ejemplos personales para complementar el contenido del curso.</t>
+        </is>
+      </c>
+      <c r="G220" s="22" t="inlineStr">
+        <is>
+          <t>El instructor incorpora ejemplos personales para complementar el contenido del curso.</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>Nivel: Entrega</t>
+        </is>
+      </c>
+      <c r="I220" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I170"/>
+  <autoFilter ref="A1:I220"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11246,18 +13615,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11268,7 +13638,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Grupo tematico</t>
+          <t>Grupo temático</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -11278,32 +13648,37 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>QM</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Sepúlveda</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Consenso</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Auto predominante</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Observacion</t>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Observación</t>
         </is>
       </c>
     </row>
@@ -11322,27 +13697,30 @@
         <v>6</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G2" s="9" t="inlineStr">
-        <is>
-          <t>3/3 fuentes</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>3</v>
+      </c>
+      <c r="G2" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>4/4 fuentes</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Alto consenso. Las 3 fuentes cubren bienvenida y orientación.</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Alto consenso (4/4). Bienvenida y orientación cubiertas por todas las fuentes.</t>
         </is>
       </c>
     </row>
@@ -11361,27 +13739,30 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>3/3 fuentes</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="G3" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>4/4 fuentes</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Alto consenso. QM tiene la cobertura más exhaustiva (5 estándares esenciales).</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Alto consenso (4/4). QM y OLC 2025 tienen cobertura más exhaustiva.</t>
         </is>
       </c>
     </row>
@@ -11400,27 +13781,30 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="F4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>3/3 fuentes</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="G4" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>4/4 fuentes</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Consenso parcial. Sepúlveda agrega protocolos IA (D6.1.2), ausentes en marcos internacionales.</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Alto consenso (4/4). OLC 2025 agrega directrices IA generativa. Sepúlveda agrega protocolos IA educativa (D6.1.2).</t>
         </is>
       </c>
     </row>
@@ -11439,27 +13823,30 @@
         <v>4</v>
       </c>
       <c r="D5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>2/3 fuentes</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="G5" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="H5" s="25" t="inlineStr">
+        <is>
+          <t>3/4 fuentes</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Consenso. OSCQR y QM cubren requisitos técnicos; Sepúlveda no aborda explícitamente.</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Consenso 3/4. Sepúlveda no aborda explícitamente. OLC 2025 agrega diagnóstico de preparación previa.</t>
         </is>
       </c>
     </row>
@@ -11478,27 +13865,30 @@
         <v>14</v>
       </c>
       <c r="D6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>3/3 fuentes</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="G6" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>4/4 fuentes</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Alto consenso. OSCQR tiene la cobertura más detallada (13 estándares de diseño).</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Alto consenso (3/4). OSCQR tiene la cobertura más detallada (13 estándares). OLC 2025 aporta 1 objetivo.</t>
         </is>
       </c>
     </row>
@@ -11517,27 +13907,30 @@
         <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>5</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>1/3 fuentes</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G7" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>2/4 fuentes</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Solo Sepúlveda. Funcionalidad técnica (botones, enlaces, pop-ups) es específica de plataforma LMS.</t>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Consenso 2/4. Sepúlveda + OLC 2025 (enlaces rotos). Funcionalidad técnica específica de plataforma LMS.</t>
         </is>
       </c>
     </row>
@@ -11556,27 +13949,30 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="F8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>3/3 fuentes</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="G8" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>4/4 fuentes</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Alto consenso. Materiales instruccionales cubiertos por las 3 fuentes.</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Alto consenso (4/4). Materiales instruccionales cubiertos por todas las fuentes.</t>
         </is>
       </c>
     </row>
@@ -11598,24 +13994,27 @@
         <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>3/3 fuentes</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="G9" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>4/4 fuentes</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Alto consenso. REA y copyright cubiertos por las 3 fuentes. Sepúlveda agrega Creative Commons y código abierto.</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Consenso 3/4. REA y copyright en OSCQR, QM y Sepúlveda. OLC 2025 agrega materiales gratuitos.</t>
         </is>
       </c>
     </row>
@@ -11634,27 +14033,30 @@
         <v>5</v>
       </c>
       <c r="D10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="F10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>3/3 fuentes</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="23" t="n">
+        <v>17</v>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>4/4 fuentes</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Alto consenso. Actividades de aprendizaje activo e interacción en las 3 fuentes.</t>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Alto consenso (4/4). OLC 2025 agrega aprendizaje adaptativo y co-creación de contenido.</t>
         </is>
       </c>
     </row>
@@ -11673,27 +14075,30 @@
         <v>7</v>
       </c>
       <c r="D11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="F11" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>3/3 fuentes</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="G11" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>4/4 fuentes</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Alto consenso. Evaluación es área central en las 3 fuentes. Sepúlveda agrega retroalimentación personalizada.</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Alto consenso (4/4). OLC 2025 tiene cobertura más amplia: andamiaje, formativas, metacognición, retroalimentación oportuna.</t>
         </is>
       </c>
     </row>
@@ -11712,27 +14117,30 @@
         <v>3</v>
       </c>
       <c r="D12" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>3/3 fuentes</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G12" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>4/4 fuentes</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Alto consenso. RSI (OSCQR) + plan docente (QM) + tutorías (Sepúlveda).</t>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Alto consenso (4/4). OLC 2025 aporta 7 objetivos de entrega docente (la mayor contribución nueva).</t>
         </is>
       </c>
     </row>
@@ -11751,27 +14159,30 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="F13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>3/3 fuentes</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="G13" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>4/4 fuentes</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Alto consenso. Soporte y servicios institucionales en las 3 fuentes.</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Alto consenso (4/4). Soporte y servicios institucionales en todas las fuentes.</t>
         </is>
       </c>
     </row>
@@ -11790,27 +14201,30 @@
         <v>4</v>
       </c>
       <c r="D14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="F14" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F14" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>3/3 fuentes</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="G14" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>4/4 fuentes</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Alto consenso. Accesibilidad cubierta ampliamente. Sepúlveda agrega lengua de signos y Braille.</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Alto consenso (4/4). OLC 2025 distingue accesibilidad de texto vs multimedia.</t>
         </is>
       </c>
     </row>
@@ -11829,27 +14243,30 @@
         <v>1</v>
       </c>
       <c r="D15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="F15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="G15" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>3/3 fuentes</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="H15" s="25" t="inlineStr">
+        <is>
+          <t>3/4 fuentes</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Consenso parcial. OSCQR y QM mencionan privacidad; Sepúlveda la desarrolla en 4 indicadores.</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Consenso 2/4. OSCQR y Sepúlveda. QM y OLC 2025 no desarrollan privacidad en profundidad.</t>
         </is>
       </c>
     </row>
@@ -11871,24 +14288,27 @@
         <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>1/3 fuentes</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G16" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>1/4 fuentes</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Solo Sepúlveda. OSCQR y QM no contemplan sesiones sincrónicas.</t>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Solo Sepúlveda. OSCQR, QM y OLC 2025 no contemplan sesiones sincrónicas.</t>
         </is>
       </c>
     </row>
@@ -11907,27 +14327,30 @@
         <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>7</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>1/3 fuentes</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G17" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>2/4 fuentes</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Solo Sepúlveda. Competencias docentes virtuales no están en marcos internacionales como dimensión propia.</t>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Consenso 2/4. Sepúlveda + OLC 2025 (entrega del curso). Competencias docentes virtuales.</t>
         </is>
       </c>
     </row>
@@ -11946,27 +14369,30 @@
         <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>5</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>1/3 fuentes</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G18" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>2/4 fuentes</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Solo Sepúlveda. Género y equidad es aporte original UMCE. Gap total en marcos internacionales.</t>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Consenso 2/4. Sepúlveda + OLC 2025 (representación diversa). Gap en OSCQR y QM.</t>
         </is>
       </c>
     </row>
@@ -11985,27 +14411,30 @@
         <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>12</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>1/3 fuentes</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G19" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>2/4 fuentes</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Solo Sepúlveda. Bienestar digital y corresponsabilidad es aporte original UMCE.</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Consenso 2/4. Sepúlveda (principal) + OLC 2025 (carga de trabajo). Bienestar y corresponsabilidad es aporte UMCE.</t>
         </is>
       </c>
     </row>
@@ -12020,7 +14449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12034,6 +14463,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -12077,173 +14507,202 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>OLC 2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OLC Course Review Scorecard (2025). Libre. 50 objetivos (20 esencial + 15 avanzado + 15 entrega). En español.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Automatizabilidad</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Automatizable: verificable vía Moodle API o scraping (ej: enlace existe, grabación disponible, syllabus presente).</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Semi-automatizable: se puede detectar presencia pero no calidad (ej: rúbrica existe, pero no si es buena).</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Requiere evaluación humana: juicio cualitativo necesario (ej: lenguaje inclusivo, retroalimentación constructiva).</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Consenso</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>3/3 fuentes</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Las tres fuentes cubren este tema. Fuerte respaldo internacional.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2/3 fuentes</t>
+          <t>3/3 fuentes</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dos fuentes cubren el tema. Respaldo parcial.</t>
+          <t>Las tres fuentes cubren este tema. Fuerte respaldo internacional.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>2/3 fuentes</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dos fuentes cubren el tema. Respaldo parcial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>1/3 fuentes</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Solo una fuente. Puede ser aporte original UMCE (D5, D6, D3.4) o especificidad de plataforma.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Colores filas</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Naranja claro</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Indicador OSCQR</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Violeta claro</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Indicador Quality Matters</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Verde claro</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Indicador Sepúlveda UMCE</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="27" t="inlineStr">
+        <is>
+          <t>Azul claro</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Indicador OLC 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>Propuesta Consolidada</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>QA-XX</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Código del indicador propuesto para el set UMCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Fuentes</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Códigos de los indicadores originales que sustentan el propuesto (ej: OSCQR-1 + QM-1.1 + D3.3.1)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>QA-XX</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Código del indicador propuesto para el set UMCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Fuentes</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Códigos de los indicadores originales que sustentan el propuesto (ej: OSCQR-1 + QM-1.1 + D3.3.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>64 indicadores</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Consolidación de 169 originales. Mesa 1 valida pertinencia y claridad de cada uno.</t>
         </is>

--- a/docs/espacio-aprendizaje/indicadores-cruce-tematico.xlsx
+++ b/docs/espacio-aprendizaje/indicadores-cruce-tematico.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leyenda" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cruce Tematico'!$A$1:$I$220</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Propuesta Consolidada'!$A$1:$G$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cruce Tematico'!$A$1:$I$242</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Propuesta Consolidada'!$A$1:$G$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -44,7 +44,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -111,6 +111,18 @@
         <bgColor rgb="00DCEDC8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+        <bgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A5D6A7"/>
+        <bgColor rgb="00A5D6A7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -130,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -197,6 +209,22 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -562,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I220"/>
+  <dimension ref="A1:I242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10915,8 +10943,1042 @@
         </is>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>Soporte al estudiante y servicios institucionales</t>
+        </is>
+      </c>
+      <c r="C221" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D221" s="28" t="inlineStr">
+        <is>
+          <t>CNA-I.1.a</t>
+        </is>
+      </c>
+      <c r="E221" s="28" t="inlineStr">
+        <is>
+          <t>Gestión Institucional</t>
+        </is>
+      </c>
+      <c r="F221" s="28" t="inlineStr">
+        <is>
+          <t>Existe una estructura institucional que entrega soporte pedagógico a los procesos de enseñanza y aprendizaje desarrollados por medio del entorno virtual de aprendizaje.</t>
+        </is>
+      </c>
+      <c r="G221" s="28" t="inlineStr">
+        <is>
+          <t>Existe una estructura institucional que entrega soporte pedagógico a los procesos de enseñanza y aprendizaje desarrollados por medio del entorno virtual de aprendizaje.</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I221" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>Soporte al estudiante y servicios institucionales</t>
+        </is>
+      </c>
+      <c r="C222" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D222" s="28" t="inlineStr">
+        <is>
+          <t>CNA-I.1.b</t>
+        </is>
+      </c>
+      <c r="E222" s="28" t="inlineStr">
+        <is>
+          <t>Gestión Institucional</t>
+        </is>
+      </c>
+      <c r="F222" s="28" t="inlineStr">
+        <is>
+          <t>Existe una estructura institucional que administra y gestiona los procesos docentes al interior del sistema de información central, entorno virtual de aprendizaje (diseño instruccional, producción de recursos, control de calidad de proveedores).</t>
+        </is>
+      </c>
+      <c r="G222" s="28" t="inlineStr">
+        <is>
+          <t>Existe una estructura institucional que administra y gestiona los procesos docentes al interior del sistema de información central, entorno virtual de aprendizaje (diseño instruccional, producción de recursos, control de calidad de proveedores).</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I222" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>Soporte al estudiante y servicios institucionales</t>
+        </is>
+      </c>
+      <c r="C223" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D223" s="28" t="inlineStr">
+        <is>
+          <t>CNA-I.1.c</t>
+        </is>
+      </c>
+      <c r="E223" s="28" t="inlineStr">
+        <is>
+          <t>Gestión Institucional</t>
+        </is>
+      </c>
+      <c r="F223" s="28" t="inlineStr">
+        <is>
+          <t>Existe una estructura institucional que entrega soporte socio-afectivo a los procesos de enseñanza y aprendizaje desarrollados por medio del entorno virtual de aprendizaje.</t>
+        </is>
+      </c>
+      <c r="G223" s="28" t="inlineStr">
+        <is>
+          <t>Existe una estructura institucional que entrega soporte socio-afectivo a los procesos de enseñanza y aprendizaje desarrollados por medio del entorno virtual de aprendizaje.</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I223" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Soporte al estudiante y servicios institucionales</t>
+        </is>
+      </c>
+      <c r="C224" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D224" s="28" t="inlineStr">
+        <is>
+          <t>CNA-I.1.d</t>
+        </is>
+      </c>
+      <c r="E224" s="28" t="inlineStr">
+        <is>
+          <t>Gestión Institucional</t>
+        </is>
+      </c>
+      <c r="F224" s="28" t="inlineStr">
+        <is>
+          <t>Existe una estructura institucional que administra, gestiona y entrega soporte técnico y mantenimiento a los medios (sistema de información central, entorno virtual de aprendizaje).</t>
+        </is>
+      </c>
+      <c r="G224" s="28" t="inlineStr">
+        <is>
+          <t>Existe una estructura institucional que administra, gestiona y entrega soporte técnico y mantenimiento a los medios (sistema de información central, entorno virtual de aprendizaje).</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I224" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>Competencias docentes para la virtualidad</t>
+        </is>
+      </c>
+      <c r="C225" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D225" s="28" t="inlineStr">
+        <is>
+          <t>CNA-I.3.b</t>
+        </is>
+      </c>
+      <c r="E225" s="28" t="inlineStr">
+        <is>
+          <t>Gestión Institucional</t>
+        </is>
+      </c>
+      <c r="F225" s="28" t="inlineStr">
+        <is>
+          <t>Para los programas en modalidad virtual, existen políticas de capacitación que permitan al personal directivo, académico y administrativo atender los requerimientos metodológicos y tecnológicos necesarios para su implementación.</t>
+        </is>
+      </c>
+      <c r="G225" s="28" t="inlineStr">
+        <is>
+          <t>Para los programas en modalidad virtual, existen políticas de capacitación que permitan al personal directivo, académico y administrativo atender los requerimientos metodológicos y tecnológicos necesarios para su implementación.</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I225" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>Funcionalidad técnica de la plataforma</t>
+        </is>
+      </c>
+      <c r="C226" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D226" s="28" t="inlineStr">
+        <is>
+          <t>CNA-I.4.a</t>
+        </is>
+      </c>
+      <c r="E226" s="28" t="inlineStr">
+        <is>
+          <t>Gestión Institucional</t>
+        </is>
+      </c>
+      <c r="F226" s="28" t="inlineStr">
+        <is>
+          <t>La universidad cuenta con infraestructura tecnológica que garantiza la calidad, continuidad y eficiencia de la implementación de programas en modalidad virtual.</t>
+        </is>
+      </c>
+      <c r="G226" s="28" t="inlineStr">
+        <is>
+          <t>La universidad cuenta con infraestructura tecnológica que garantiza la calidad, continuidad y eficiencia de la implementación de programas en modalidad virtual.</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I226" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>Funcionalidad técnica de la plataforma</t>
+        </is>
+      </c>
+      <c r="C227" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D227" s="28" t="inlineStr">
+        <is>
+          <t>CNA-I.4.c</t>
+        </is>
+      </c>
+      <c r="E227" s="28" t="inlineStr">
+        <is>
+          <t>Gestión Institucional</t>
+        </is>
+      </c>
+      <c r="F227" s="28" t="inlineStr">
+        <is>
+          <t>Existen mecanismos para asegurar la disponibilidad continua de servicios informáticos y conectividad de calidad.</t>
+        </is>
+      </c>
+      <c r="G227" s="28" t="inlineStr">
+        <is>
+          <t>Existen mecanismos para asegurar la disponibilidad continua de servicios informáticos y conectividad de calidad.</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I227" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>Evaluación, retroalimentación y calificaciones</t>
+        </is>
+      </c>
+      <c r="C228" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D228" s="28" t="inlineStr">
+        <is>
+          <t>CNA-I.5.c</t>
+        </is>
+      </c>
+      <c r="E228" s="28" t="inlineStr">
+        <is>
+          <t>Gestión Institucional</t>
+        </is>
+      </c>
+      <c r="F228" s="28" t="inlineStr">
+        <is>
+          <t>La institución utiliza mecanismos formales y sistemáticos de evaluación y monitoreo de sus procesos y resultados asociados a la modalidad virtual, los que incluyen indicadores cuantitativos y cualitativos asociados a esta.</t>
+        </is>
+      </c>
+      <c r="G228" s="28" t="inlineStr">
+        <is>
+          <t>La institución utiliza mecanismos formales y sistemáticos de evaluación y monitoreo de sus procesos y resultados asociados a la modalidad virtual, los que incluyen indicadores cuantitativos y cualitativos asociados a esta.</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I228" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>Políticas institucionales y normas académicas</t>
+        </is>
+      </c>
+      <c r="C229" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D229" s="28" t="inlineStr">
+        <is>
+          <t>CNA-I.5.e</t>
+        </is>
+      </c>
+      <c r="E229" s="28" t="inlineStr">
+        <is>
+          <t>Gestión Institucional</t>
+        </is>
+      </c>
+      <c r="F229" s="28" t="inlineStr">
+        <is>
+          <t>La universidad cuenta con reglamentación específica de derechos y deberes para los estudiantes de la modalidad virtual (carga académica, calificaciones, normas de admisión).</t>
+        </is>
+      </c>
+      <c r="G229" s="28" t="inlineStr">
+        <is>
+          <t>La universidad cuenta con reglamentación específica de derechos y deberes para los estudiantes de la modalidad virtual (carga académica, calificaciones, normas de admisión).</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I229" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>Políticas institucionales y normas académicas</t>
+        </is>
+      </c>
+      <c r="C230" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D230" s="28" t="inlineStr">
+        <is>
+          <t>CNA-I.5.f</t>
+        </is>
+      </c>
+      <c r="E230" s="28" t="inlineStr">
+        <is>
+          <t>Gestión Institucional</t>
+        </is>
+      </c>
+      <c r="F230" s="28" t="inlineStr">
+        <is>
+          <t>La normativa institucional recoge las características de la modalidad virtual en aspectos tales como probidad, acceso, apoyo tutorial, requerimientos técnicos y competencias digitales del usuario.</t>
+        </is>
+      </c>
+      <c r="G230" s="28" t="inlineStr">
+        <is>
+          <t>La normativa institucional recoge las características de la modalidad virtual en aspectos tales como probidad, acceso, apoyo tutorial, requerimientos técnicos y competencias digitales del usuario.</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I230" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>Accesibilidad multimodal y DUA</t>
+        </is>
+      </c>
+      <c r="C231" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D231" s="28" t="inlineStr">
+        <is>
+          <t>CNA-II.1.d</t>
+        </is>
+      </c>
+      <c r="E231" s="28" t="inlineStr">
+        <is>
+          <t>Docencia Pregrado</t>
+        </is>
+      </c>
+      <c r="F231" s="28" t="inlineStr">
+        <is>
+          <t>La institución debe disponer de políticas y mecanismos eficaces para asegurar la calidad de las carreras que ofrece en la modalidad virtual (diseño instruccional, condiciones de accesibilidad, acceso desde múltiples dispositivos).</t>
+        </is>
+      </c>
+      <c r="G231" s="28" t="inlineStr">
+        <is>
+          <t>La institución debe disponer de políticas y mecanismos eficaces para asegurar la calidad de las carreras que ofrece en la modalidad virtual (diseño instruccional, condiciones de accesibilidad, acceso desde múltiples dispositivos).</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I231" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>Objetivos y resultados de aprendizaje</t>
+        </is>
+      </c>
+      <c r="C232" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D232" s="28" t="inlineStr">
+        <is>
+          <t>CNA-II.1.e</t>
+        </is>
+      </c>
+      <c r="E232" s="28" t="inlineStr">
+        <is>
+          <t>Docencia Pregrado</t>
+        </is>
+      </c>
+      <c r="F232" s="28" t="inlineStr">
+        <is>
+          <t>Las carreras o programas impartidos en modalidad virtual presentan mecanismos que aseguran que los estudiantes logren los conocimientos, competencias y habilidades declaradas en el perfil de egreso.</t>
+        </is>
+      </c>
+      <c r="G232" s="28" t="inlineStr">
+        <is>
+          <t>Las carreras o programas impartidos en modalidad virtual presentan mecanismos que aseguran que los estudiantes logren los conocimientos, competencias y habilidades declaradas en el perfil de egreso.</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I232" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>Contenidos y materiales instruccionales</t>
+        </is>
+      </c>
+      <c r="C233" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D233" s="28" t="inlineStr">
+        <is>
+          <t>CNA-II.2.a</t>
+        </is>
+      </c>
+      <c r="E233" s="28" t="inlineStr">
+        <is>
+          <t>Docencia Pregrado</t>
+        </is>
+      </c>
+      <c r="F233" s="28" t="inlineStr">
+        <is>
+          <t>La institución cuenta con al menos un modelo instruccional para la modalidad virtual, claro y conocido por docentes y estudiantes, para el diseño de un entorno virtual de aprendizaje.</t>
+        </is>
+      </c>
+      <c r="G233" s="28" t="inlineStr">
+        <is>
+          <t>La institución cuenta con al menos un modelo instruccional para la modalidad virtual, claro y conocido por docentes y estudiantes, para el diseño de un entorno virtual de aprendizaje.</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I233" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>Navegación, diseño y estructura visual</t>
+        </is>
+      </c>
+      <c r="C234" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D234" s="28" t="inlineStr">
+        <is>
+          <t>CNA-II.2.b</t>
+        </is>
+      </c>
+      <c r="E234" s="28" t="inlineStr">
+        <is>
+          <t>Docencia Pregrado</t>
+        </is>
+      </c>
+      <c r="F234" s="28" t="inlineStr">
+        <is>
+          <t>La institución debe contar con un entorno virtual de aprendizaje que responda a los requerimientos explicitados en el modelo instruccional para la implementación de procesos de enseñanza, aprendizaje y evaluación centrados en el estudiante.</t>
+        </is>
+      </c>
+      <c r="G234" s="28" t="inlineStr">
+        <is>
+          <t>La institución debe contar con un entorno virtual de aprendizaje que responda a los requerimientos explicitados en el modelo instruccional para la implementación de procesos de enseñanza, aprendizaje y evaluación centrados en el estudiante.</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I234" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>Evaluación, retroalimentación y calificaciones</t>
+        </is>
+      </c>
+      <c r="C235" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D235" s="28" t="inlineStr">
+        <is>
+          <t>CNA-II.2.c</t>
+        </is>
+      </c>
+      <c r="E235" s="28" t="inlineStr">
+        <is>
+          <t>Docencia Pregrado</t>
+        </is>
+      </c>
+      <c r="F235" s="28" t="inlineStr">
+        <is>
+          <t>La institución debe disponer de mecanismos efectivos, eficientes y seguros para la evaluación de los aprendizajes de los estudiantes, incluyendo aspectos tales como la identidad de los estudiantes y el control de plagio.</t>
+        </is>
+      </c>
+      <c r="G235" s="28" t="inlineStr">
+        <is>
+          <t>La institución debe disponer de mecanismos efectivos, eficientes y seguros para la evaluación de los aprendizajes de los estudiantes, incluyendo aspectos tales como la identidad de los estudiantes y el control de plagio.</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I235" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>Competencias docentes para la virtualidad</t>
+        </is>
+      </c>
+      <c r="C236" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D236" s="28" t="inlineStr">
+        <is>
+          <t>CNA-II.3.a</t>
+        </is>
+      </c>
+      <c r="E236" s="28" t="inlineStr">
+        <is>
+          <t>Docencia Pregrado</t>
+        </is>
+      </c>
+      <c r="F236" s="28" t="inlineStr">
+        <is>
+          <t>La universidad cuenta con una estructura docente adecuada que responde a las necesidades de enseñanza, apoyo y retroalimentación propios de la modalidad virtual, incluyendo a docentes y tutores.</t>
+        </is>
+      </c>
+      <c r="G236" s="28" t="inlineStr">
+        <is>
+          <t>La universidad cuenta con una estructura docente adecuada que responde a las necesidades de enseñanza, apoyo y retroalimentación propios de la modalidad virtual, incluyendo a docentes y tutores.</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I236" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>Competencias docentes para la virtualidad</t>
+        </is>
+      </c>
+      <c r="C237" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D237" s="28" t="inlineStr">
+        <is>
+          <t>CNA-II.3.c</t>
+        </is>
+      </c>
+      <c r="E237" s="28" t="inlineStr">
+        <is>
+          <t>Docencia Pregrado</t>
+        </is>
+      </c>
+      <c r="F237" s="28" t="inlineStr">
+        <is>
+          <t>Los procesos de perfeccionamiento abordan aspectos relacionados con la construcción, dictación, tutorización y coordinación de programas en modalidad virtual.</t>
+        </is>
+      </c>
+      <c r="G237" s="28" t="inlineStr">
+        <is>
+          <t>Los procesos de perfeccionamiento abordan aspectos relacionados con la construcción, dictación, tutorización y coordinación de programas en modalidad virtual.</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I237" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>T01</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>Bienvenida, orientación e información del curso</t>
+        </is>
+      </c>
+      <c r="C238" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D238" s="28" t="inlineStr">
+        <is>
+          <t>CNA-II.4.a</t>
+        </is>
+      </c>
+      <c r="E238" s="28" t="inlineStr">
+        <is>
+          <t>Docencia Pregrado</t>
+        </is>
+      </c>
+      <c r="F238" s="28" t="inlineStr">
+        <is>
+          <t>La institución debe contar con mecanismos de inducción y acogida para sus estudiantes, vinculados a la preparación y apropiación de las herramientas y metodologías asociadas a programas en modalidad virtual.</t>
+        </is>
+      </c>
+      <c r="G238" s="28" t="inlineStr">
+        <is>
+          <t>La institución debe contar con mecanismos de inducción y acogida para sus estudiantes, vinculados a la preparación y apropiación de las herramientas y metodologías asociadas a programas en modalidad virtual.</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I238" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>Soporte al estudiante y servicios institucionales</t>
+        </is>
+      </c>
+      <c r="C239" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D239" s="28" t="inlineStr">
+        <is>
+          <t>CNA-II.4.b</t>
+        </is>
+      </c>
+      <c r="E239" s="28" t="inlineStr">
+        <is>
+          <t>Docencia Pregrado</t>
+        </is>
+      </c>
+      <c r="F239" s="28" t="inlineStr">
+        <is>
+          <t>La institución debe disponer de estrategias para el apoyo técnico, académico y socio-afectivo de los estudiantes que participan de la modalidad virtual.</t>
+        </is>
+      </c>
+      <c r="G239" s="28" t="inlineStr">
+        <is>
+          <t>La institución debe disponer de estrategias para el apoyo técnico, académico y socio-afectivo de los estudiantes que participan de la modalidad virtual.</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I239" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>Funcionalidad técnica de la plataforma</t>
+        </is>
+      </c>
+      <c r="C240" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D240" s="28" t="inlineStr">
+        <is>
+          <t>CNA-II.4.d</t>
+        </is>
+      </c>
+      <c r="E240" s="28" t="inlineStr">
+        <is>
+          <t>Docencia Pregrado</t>
+        </is>
+      </c>
+      <c r="F240" s="28" t="inlineStr">
+        <is>
+          <t>La institución debe contar con una adecuada plataforma informática, que permita entregar el servicio de manera continua y apropiada a los estudiantes que participan de la modalidad virtual.</t>
+        </is>
+      </c>
+      <c r="G240" s="28" t="inlineStr">
+        <is>
+          <t>La institución debe contar con una adecuada plataforma informática, que permita entregar el servicio de manera continua y apropiada a los estudiantes que participan de la modalidad virtual.</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I240" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>Evaluación, retroalimentación y calificaciones</t>
+        </is>
+      </c>
+      <c r="C241" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D241" s="28" t="inlineStr">
+        <is>
+          <t>CNA-II.4.e</t>
+        </is>
+      </c>
+      <c r="E241" s="28" t="inlineStr">
+        <is>
+          <t>Docencia Pregrado</t>
+        </is>
+      </c>
+      <c r="F241" s="28" t="inlineStr">
+        <is>
+          <t>La institución debe disponer de mecanismos para el monitoreo y seguimiento de la participación y aprendizaje de los estudiantes que participan de la modalidad virtual.</t>
+        </is>
+      </c>
+      <c r="G241" s="28" t="inlineStr">
+        <is>
+          <t>La institución debe disponer de mecanismos para el monitoreo y seguimiento de la participación y aprendizaje de los estudiantes que participan de la modalidad virtual.</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I241" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>Actividades de aprendizaje e interacción</t>
+        </is>
+      </c>
+      <c r="C242" s="28" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="D242" s="28" t="inlineStr">
+        <is>
+          <t>CNA-II.5</t>
+        </is>
+      </c>
+      <c r="E242" s="28" t="inlineStr">
+        <is>
+          <t>Docencia Pregrado</t>
+        </is>
+      </c>
+      <c r="F242" s="28" t="inlineStr">
+        <is>
+          <t>La universidad incentiva y evidencia los aportes de investigación y desarrollo, propios o de terceros, en la modalidad virtual particularmente en los ámbitos de retención de estudiantes, diseño de materiales digitales, innovación de las evaluaciones, diseño de actividades centradas en el estudiante.</t>
+        </is>
+      </c>
+      <c r="G242" s="28" t="inlineStr">
+        <is>
+          <t>La universidad incentiva y evidencia los aportes de investigación y desarrollo, propios o de terceros, en la modalidad virtual particularmente en los ámbitos de retención de estudiantes, diseño de materiales digitales, innovación de las evaluaciones, diseño de actividades centradas en el estudiante.</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>Orientación CNA modalidad virtual</t>
+        </is>
+      </c>
+      <c r="I242" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I220"/>
+  <autoFilter ref="A1:I242"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10927,7 +11989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13603,8 +14665,156 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>QA-72</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Evaluación, retroalimentación y calificaciones</t>
+        </is>
+      </c>
+      <c r="D73" s="28" t="inlineStr">
+        <is>
+          <t>El curso dispone de mecanismos para verificar la identidad de los estudiantes durante las evaluaciones y para prevenir el plagio (control de originalidad, supervisión en línea u otros).</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>CNA-II.2.c [GAP cubierto]</t>
+        </is>
+      </c>
+      <c r="F73" s="29" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>QA-73</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Políticas institucionales y normas académicas</t>
+        </is>
+      </c>
+      <c r="D74" s="28" t="inlineStr">
+        <is>
+          <t>El curso incluye un enlace visible al reglamento institucional de la modalidad virtual, que establece derechos y deberes de los estudiantes, normativa de evaluación, carga académica y condiciones de la modalidad.</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>CNA-I.5.e,I.5.f [GAP cubierto]</t>
+        </is>
+      </c>
+      <c r="F74" s="29" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>QA-74</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Soporte al estudiante y servicios institucionales</t>
+        </is>
+      </c>
+      <c r="D75" s="28" t="inlineStr">
+        <is>
+          <t>El curso proporciona información y acceso a servicios de apoyo integral al estudiante: soporte técnico, orientación académica, apoyo socio-afectivo y derivación a servicios institucionales (bienestar, salud mental, asuntos estudiantiles).</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>CNA-I.1.c,II.4.b [GAP cubierto]</t>
+        </is>
+      </c>
+      <c r="F75" s="29" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>QA-75</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Funcionalidad técnica de la plataforma</t>
+        </is>
+      </c>
+      <c r="D76" s="28" t="inlineStr">
+        <is>
+          <t>El curso informa un protocolo de contingencia técnica: qué hacer ante caídas de plataforma, pérdida de conectividad o problemas de acceso durante actividades evaluativas.</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>CNA-I.4.a,I.4.c [GAP cubierto]</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G72"/>
+  <autoFilter ref="A1:G76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13615,19 +14825,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13663,20 +14874,25 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>CNA</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Consenso</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
@@ -13706,21 +14922,24 @@
         <v>3</v>
       </c>
       <c r="G2" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="H2" s="9" t="inlineStr">
-        <is>
-          <t>4/4 fuentes</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>1</v>
+      </c>
+      <c r="H2" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="I2" s="31" t="inlineStr">
+        <is>
+          <t>5/5 fuentes</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Alto consenso (4/4). Bienvenida y orientación cubiertas por todas las fuentes.</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Alto consenso (5/5). Bienvenida y orientación cubiertas por todas las fuentes. CNA exige inducción a herramientas virtuales (II.4.a).</t>
         </is>
       </c>
     </row>
@@ -13748,21 +14967,24 @@
         <v>1</v>
       </c>
       <c r="G3" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>4/4 fuentes</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>1</v>
+      </c>
+      <c r="H3" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" s="31" t="inlineStr">
+        <is>
+          <t>5/5 fuentes</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Alto consenso (4/4). QM y OLC 2025 tienen cobertura más exhaustiva.</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Alto consenso (5/5). CNA exige mecanismos para asegurar logro del perfil de egreso (II.1.e).</t>
         </is>
       </c>
     </row>
@@ -13790,21 +15012,24 @@
         <v>2</v>
       </c>
       <c r="G4" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>4/4 fuentes</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>2</v>
+      </c>
+      <c r="H4" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" s="31" t="inlineStr">
+        <is>
+          <t>5/5 fuentes</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Alto consenso (4/4). OLC 2025 agrega directrices IA generativa. Sepúlveda agrega protocolos IA educativa (D6.1.2).</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Alto consenso (5/5). CNA es la fuente más exigente: reglamento de virtualidad + normativa de derechos/deberes + probidad + competencias digitales.</t>
         </is>
       </c>
     </row>
@@ -13832,21 +15057,24 @@
         <v>0</v>
       </c>
       <c r="G5" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="32" t="n">
         <v>11</v>
       </c>
-      <c r="H5" s="25" t="inlineStr">
-        <is>
-          <t>3/4 fuentes</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="I5" s="25" t="inlineStr">
+        <is>
+          <t>3/5 fuentes</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Consenso 3/4. Sepúlveda no aborda explícitamente. OLC 2025 agrega diagnóstico de preparación previa.</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Consenso 3/5. Sepúlveda y CNA no abordan explícitamente requisitos tecnológicos del estudiante.</t>
         </is>
       </c>
     </row>
@@ -13874,21 +15102,24 @@
         <v>9</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>26</v>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>4/4 fuentes</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>1</v>
+      </c>
+      <c r="H6" s="23" t="n">
+        <v>27</v>
+      </c>
+      <c r="I6" s="31" t="inlineStr">
+        <is>
+          <t>5/5 fuentes</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Alto consenso (3/4). OSCQR tiene la cobertura más detallada (13 estándares). OLC 2025 aporta 1 objetivo.</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Consenso 4/5. CNA exige entorno virtual que responda al modelo instruccional (II.2.b).</t>
         </is>
       </c>
     </row>
@@ -13916,21 +15147,24 @@
         <v>5</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>2/4 fuentes</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="H7" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="I7" s="25" t="inlineStr">
+        <is>
+          <t>3/5 fuentes</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Consenso 2/4. Sepúlveda + OLC 2025 (enlaces rotos). Funcionalidad técnica específica de plataforma LMS.</t>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Consenso 3/5. CNA aporta infraestructura, continuidad y contingencia técnica. Sepúlveda aporta funcionalidad LMS.</t>
         </is>
       </c>
     </row>
@@ -13958,21 +15192,24 @@
         <v>2</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>4/4 fuentes</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>1</v>
+      </c>
+      <c r="H8" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="I8" s="31" t="inlineStr">
+        <is>
+          <t>5/5 fuentes</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Alto consenso (4/4). Materiales instruccionales cubiertos por todas las fuentes.</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Alto consenso (5/5). CNA exige modelo instruccional claro y conocido (II.2.a).</t>
         </is>
       </c>
     </row>
@@ -14000,21 +15237,24 @@
         <v>4</v>
       </c>
       <c r="G9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>4/4 fuentes</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>4/5 fuentes</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Consenso 3/4. REA y copyright en OSCQR, QM y Sepúlveda. OLC 2025 agrega materiales gratuitos.</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Consenso 3/5. REA y copyright en OSCQR, QM y Sepúlveda.</t>
         </is>
       </c>
     </row>
@@ -14042,21 +15282,24 @@
         <v>2</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>4/4 fuentes</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="I10" s="31" t="inlineStr">
+        <is>
+          <t>5/5 fuentes</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Alto consenso (4/4). OLC 2025 agrega aprendizaje adaptativo y co-creación de contenido.</t>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Alto consenso (5/5). CNA incentiva investigación en diseño de actividades centradas en el estudiante (II.5).</t>
         </is>
       </c>
     </row>
@@ -14084,21 +15327,24 @@
         <v>4</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>26</v>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>4/4 fuentes</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>3</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <v>29</v>
+      </c>
+      <c r="I11" s="31" t="inlineStr">
+        <is>
+          <t>5/5 fuentes</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Alto consenso (4/4). OLC 2025 tiene cobertura más amplia: andamiaje, formativas, metacognición, retroalimentación oportuna.</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Alto consenso (5/5). CNA aporta verificación de identidad + control de plagio (II.2.c) y monitoreo de participación (II.4.e).</t>
         </is>
       </c>
     </row>
@@ -14126,21 +15372,24 @@
         <v>1</v>
       </c>
       <c r="G12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>4/4 fuentes</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>4/5 fuentes</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Alto consenso (4/4). OLC 2025 aporta 7 objetivos de entrega docente (la mayor contribución nueva).</t>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Consenso 4/5. CNA no tiene criterios específicos de presencia docente activa a nivel de curso.</t>
         </is>
       </c>
     </row>
@@ -14168,21 +15417,24 @@
         <v>3</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>4/4 fuentes</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>5</v>
+      </c>
+      <c r="H13" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="I13" s="31" t="inlineStr">
+        <is>
+          <t>5/5 fuentes</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Alto consenso (4/4). Soporte y servicios institucionales en todas las fuentes.</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Alto consenso (5/5). CNA es la fuente más completa: soporte pedagógico + técnico + socio-afectivo + servicios estudiantiles.</t>
         </is>
       </c>
     </row>
@@ -14210,21 +15462,24 @@
         <v>8</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>19</v>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>4/4 fuentes</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>1</v>
+      </c>
+      <c r="H14" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="I14" s="31" t="inlineStr">
+        <is>
+          <t>5/5 fuentes</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Alto consenso (4/4). OLC 2025 distingue accesibilidad de texto vs multimedia.</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Consenso 4/5. CNA exige accesibilidad y acceso multi-dispositivo (II.1.d).</t>
         </is>
       </c>
     </row>
@@ -14252,21 +15507,24 @@
         <v>4</v>
       </c>
       <c r="G15" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="H15" s="25" t="inlineStr">
-        <is>
-          <t>3/4 fuentes</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="I15" s="25" t="inlineStr">
+        <is>
+          <t>3/5 fuentes</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Consenso 2/4. OSCQR y Sepúlveda. QM y OLC 2025 no desarrollan privacidad en profundidad.</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Consenso 3/5. OSCQR, QM y Sepúlveda. CNA no desarrolla privacidad de datos a nivel curso.</t>
         </is>
       </c>
     </row>
@@ -14294,21 +15552,24 @@
         <v>5</v>
       </c>
       <c r="G16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>1/4 fuentes</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>1/5 fuentes</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>Solo Sepúlveda. OSCQR, QM y OLC 2025 no contemplan sesiones sincrónicas.</t>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Solo Sepúlveda. Ningún marco internacional ni CNA contempla sesiones sincrónicas explícitamente.</t>
         </is>
       </c>
     </row>
@@ -14336,21 +15597,24 @@
         <v>7</v>
       </c>
       <c r="G17" s="26" t="n">
-        <v>11</v>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>2/4 fuentes</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
+        <is>
+          <t>3/5 fuentes</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>Consenso 2/4. Sepúlveda + OLC 2025 (entrega del curso). Competencias docentes virtuales.</t>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Alto consenso (4/5). CNA exige capacitación docente + perfeccionamiento en construcción/dictación/tutorización virtual (I.3.b, II.3.a, II.3.c).</t>
         </is>
       </c>
     </row>
@@ -14378,21 +15642,24 @@
         <v>5</v>
       </c>
       <c r="G18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>2/4 fuentes</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>2/5 fuentes</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>Consenso 2/4. Sepúlveda + OLC 2025 (representación diversa). Gap en OSCQR y QM.</t>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Consenso 2/5. Sepúlveda + OLC 2025 (representación diversa). CNA, OSCQR y QM no abordan género.</t>
         </is>
       </c>
     </row>
@@ -14420,21 +15687,24 @@
         <v>12</v>
       </c>
       <c r="G19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="24" t="n">
         <v>13</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>2/4 fuentes</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>2/5 fuentes</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>Consenso 2/4. Sepúlveda (principal) + OLC 2025 (carga de trabajo). Bienestar y corresponsabilidad es aporte UMCE.</t>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Consenso 3/5. Sepúlveda (principal) + OLC 2025 (carga) + CNA (carga académica en reglamento I.5.e).</t>
         </is>
       </c>
     </row>
@@ -14449,7 +15719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14463,7 +15733,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -14519,7 +15788,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
@@ -14563,7 +15831,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
@@ -14607,7 +15874,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
@@ -14663,8 +15929,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
@@ -14705,6 +15969,42 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>Consolidación de 169 originales. Mesa 1 valida pertinencia y claridad de cada uno.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>CNA Chile (5ta fuente)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="33" t="inlineStr">
+        <is>
+          <t>CNA Chile</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Orientaciones CNA para acreditación de instituciones con programas en modalidad virtual y combinada — Universidades. Documento de trabajo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="33" t="inlineStr">
+        <is>
+          <t>Verde oscuro</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Indicador CNA Chile</t>
         </is>
       </c>
     </row>

--- a/docs/espacio-aprendizaje/indicadores-cruce-tematico.xlsx
+++ b/docs/espacio-aprendizaje/indicadores-cruce-tematico.xlsx
@@ -1086,7 +1086,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D148" s="7" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="C150" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D150" s="7" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="C151" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="C152" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D152" s="7" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="C153" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="C155" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="C156" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D156" s="7" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C157" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="C158" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D158" s="7" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C159" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="C160" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D160" s="7" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="C161" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="C162" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D162" s="7" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="C164" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D164" s="7" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="C165" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="C166" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D166" s="7" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="C167" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D167" s="7" t="inlineStr">
@@ -8465,7 +8465,7 @@
       </c>
       <c r="C168" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D168" s="7" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="C170" s="7" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="D170" s="7" t="inlineStr">
@@ -15733,6 +15733,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -15767,12 +15768,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sepúlveda UMCE</t>
+          <t>UDFV-UMCE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Marco Evaluativo Cursos Virtuales UMCE (2024). UMC20992. 77 indicadores.</t>
+          <t>Marco Evaluativo Cursos Virtuales UMCE (2024). UMC21992. 77 indicadores.</t>
         </is>
       </c>
     </row>
@@ -15788,6 +15789,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
@@ -15831,6 +15833,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
@@ -15874,6 +15877,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
@@ -15913,7 +15917,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Indicador Sepúlveda UMCE</t>
+          <t>Indicador UDFV-UMCE</t>
         </is>
       </c>
     </row>
@@ -15929,6 +15933,8 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
@@ -15972,17 +15978,14 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-    </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
           <t>CNA Chile (5ta fuente)</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="33" t="inlineStr">
